--- a/02_Zero_Shot/outputs/Embedding/XLNet-base-cased/RESULT_pan_xlnet-base-cased_zeroshot.xlsx
+++ b/02_Zero_Shot/outputs/Embedding/XLNet-base-cased/RESULT_pan_xlnet-base-cased_zeroshot.xlsx
@@ -24159,7 +24159,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.170840419000342</v>
+        <v>26.10277363500063</v>
       </c>
     </row>
     <row r="8">
@@ -24169,7 +24169,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.005158877999280821</v>
+        <v>0.01877897383812995</v>
       </c>
     </row>
   </sheetData>
